--- a/kawasaki_project/05_試算・管理シート/川崎町_事業の内容の出所_R8.10.4.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_事業の内容の出所_R8.10.4.xlsx
@@ -4745,40 +4745,40 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>6-4</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr"/>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="B113" s="6" t="inlineStr"/>
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>（３）実施状況の評価と結果の公表</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D113" s="6" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
-        <is>
-          <t>保健福祉課</t>
-        </is>
-      </c>
-      <c r="F113" s="5" t="inlineStr">
-        <is>
-          <t>② 統合体系表（新規・拡充）</t>
-        </is>
-      </c>
-      <c r="G113" s="5" t="inlineStr">
-        <is>
-          <t>交付金の評価指標「進捗状況の評価に当たり認知症の当事者の意見を聴いているか」と同内容（確認事項No.93）</t>
-        </is>
-      </c>
-      <c r="H113" s="5" t="inlineStr">
-        <is>
-          <t>統合体系表 03シートの「第10期での内容」による。</t>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>保健福祉課</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>③ 当方が書き起こした</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>計画の実施状況を毎年度評価し、結果を公表します。評価にあたっては、認知症の人及び家族等の意見を聴きます（認知症基本法第12条第5項）。</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法・国の指針が内容を定めているもの、又は素案の本文に記述があるもの。**実際の運用と食い違っていないかご確認ください。**</t>
         </is>
       </c>
     </row>
@@ -5323,44 +5323,44 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A128" s="6" t="inlineStr">
         <is>
           <t>6-4</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="6" t="inlineStr">
         <is>
           <t>１　認知症サポーター活動促進・地域づくりの推進（法第14条）</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C128" s="6" t="inlineStr">
         <is>
           <t>（１）認知症サポーター養成講座の開催</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D128" s="6" t="inlineStr">
         <is>
           <t>拡充</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>保健福祉課</t>
-        </is>
-      </c>
-      <c r="F128" s="5" t="inlineStr">
-        <is>
-          <t>② 統合体系表（新規・拡充）</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="inlineStr">
-        <is>
-          <t>町提供データの累計642人との食い違いを確認中（確認事項No.94）</t>
-        </is>
-      </c>
-      <c r="H128" s="5" t="inlineStr">
-        <is>
-          <t>統合体系表 03シートの「第10期での内容」による。</t>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>保健福祉課</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>③ 当方が書き起こした</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>認知症について正しく理解し、認知症の人と家族を見守る応援者を養成する講座を開きます。</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法・国の指針が内容を定めているもの、又は素案の本文に記述があるもの。**実際の運用と食い違っていないかご確認ください。**</t>
         </is>
       </c>
     </row>
@@ -5517,82 +5517,82 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="inlineStr">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>6-4</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>１　社会参加の機会の確保（法第16条）</t>
         </is>
       </c>
-      <c r="C133" s="5" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
         <is>
           <t>（１）認知症本人ミーティングの開催</t>
         </is>
       </c>
-      <c r="D133" s="5" t="inlineStr">
+      <c r="D133" s="6" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
-      <c r="E133" s="5" t="inlineStr">
+      <c r="E133" s="6" t="inlineStr">
         <is>
           <t>地域包括支援センター</t>
         </is>
       </c>
-      <c r="F133" s="5" t="inlineStr">
-        <is>
-          <t>② 統合体系表（新規・拡充）</t>
-        </is>
-      </c>
-      <c r="G133" s="5" t="inlineStr">
-        <is>
-          <t>体系（案）に対応する事業がなかった（確認事項No.112）</t>
-        </is>
-      </c>
-      <c r="H133" s="5" t="inlineStr">
-        <is>
-          <t>統合体系表 03シートの「第10期での内容」による。</t>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>③ 当方が書き起こした</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>認知症の本人が集まり、自らの体験や希望を語り合う場を設けます（第10期に新設）。</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法・国の指針が内容を定めているもの、又は素案の本文に記述があるもの。**実際の運用と食い違っていないかご確認ください。**</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="inlineStr">
+      <c r="A134" s="6" t="inlineStr">
         <is>
           <t>6-4</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr"/>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="B134" s="6" t="inlineStr"/>
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>（２）若年性認知症の人の就労継続に関する事業主への啓発</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D134" s="6" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
-      <c r="E134" s="5" t="inlineStr">
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>保健福祉課・企画課</t>
         </is>
       </c>
-      <c r="F134" s="5" t="inlineStr">
-        <is>
-          <t>② 統合体系表（新規・拡充）</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="inlineStr">
-        <is>
-          <t>町における該当者の把握状況とあわせて確認中（確認事項No.95）</t>
-        </is>
-      </c>
-      <c r="H134" s="5" t="inlineStr">
-        <is>
-          <t>統合体系表 03シートの「第10期での内容」による。</t>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>③ 当方が書き起こした</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>65歳未満で認知症を発症した方が働き続けられるよう、事業主への啓発を行います。</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法・国の指針が内容を定めているもの、又は素案の本文に記述があるもの。**実際の運用と食い違っていないかご確認ください。**</t>
         </is>
       </c>
     </row>
@@ -5753,44 +5753,44 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="inlineStr">
+      <c r="A139" s="6" t="inlineStr">
         <is>
           <t>6-4</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B139" s="6" t="inlineStr">
         <is>
           <t>３　調査研究の成果の活用（法第20条）</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C139" s="6" t="inlineStr">
         <is>
           <t>（１）国の研究成果の活用と普及</t>
         </is>
       </c>
-      <c r="D139" s="5" t="inlineStr">
+      <c r="D139" s="6" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
-      <c r="E139" s="5" t="inlineStr">
-        <is>
-          <t>保健福祉課</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="inlineStr">
-        <is>
-          <t>② 統合体系表（新規・拡充）</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="inlineStr">
-        <is>
-          <t>体系（案）に対応する事業がなかった（確認事項No.112）</t>
-        </is>
-      </c>
-      <c r="H139" s="5" t="inlineStr">
-        <is>
-          <t>統合体系表 03シートの「第10期での内容」による。</t>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>保健福祉課</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>③ 当方が書き起こした</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>認知症に関する国の研究の成果を、町の施策と住民への情報提供に活かします。</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法・国の指針が内容を定めているもの、又は素案の本文に記述があるもの。**実際の運用と食い違っていないかご確認ください。**</t>
         </is>
       </c>
     </row>
@@ -5958,7 +5958,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -5968,7 +5968,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
